--- a/public/exports-with-coowners/29188505.xlsx
+++ b/public/exports-with-coowners/29188505.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558842</t>
+          <t xml:space="preserve">311558846</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">

--- a/public/exports-with-coowners/29188505.xlsx
+++ b/public/exports-with-coowners/29188505.xlsx
@@ -14764,7 +14764,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558846</t>
+          <t xml:space="preserve">311558842</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558830</t>
+          <t xml:space="preserve">311558842</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -23314,12 +23314,12 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876582</t>
+          <t xml:space="preserve">311876603</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energiingeniørerne ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M311" t="inlineStr">

--- a/public/exports-with-coowners/29188505.xlsx
+++ b/public/exports-with-coowners/29188505.xlsx
@@ -14839,7 +14839,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558842</t>
+          <t xml:space="preserve">311558830</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -23314,12 +23314,12 @@
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">311876603</t>
+          <t xml:space="preserve">311876582</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energiingeniørerne ApS</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
